--- a/Pruebas calificadas/COLEGIO-DELIA-ZAPATA-OLIVELLA-(IED)-}1105_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-DELIA-ZAPATA-OLIVELLA-(IED)-}1105_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,11 +2048,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -2080,7 +2056,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -2333,7 +2305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -2839,7 +2803,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -3092,7 +3052,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -3345,7 +3301,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -3851,7 +3799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -4104,7 +4048,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -4357,7 +4297,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -4610,7 +4546,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -4863,7 +4795,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -5116,7 +5044,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -5369,7 +5293,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -5622,7 +5542,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -5875,7 +5791,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -6128,7 +6040,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -6381,7 +6289,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6622,11 +6530,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -6634,7 +6538,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6875,11 +6779,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -6887,7 +6787,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7128,11 +7028,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -7140,7 +7036,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7381,11 +7277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -7393,7 +7285,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7634,11 +7526,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -7646,7 +7534,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7887,11 +7775,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -7899,7 +7783,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8140,11 +8024,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -8152,7 +8032,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8393,11 +8273,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -8405,7 +8281,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8646,11 +8522,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -8658,7 +8530,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8899,11 +8771,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -8911,7 +8779,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9152,11 +9020,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -9164,7 +9028,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9405,11 +9269,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -9417,7 +9277,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9658,11 +9518,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -9670,7 +9526,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9911,11 +9767,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -9923,7 +9775,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10164,11 +10016,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -10176,7 +10024,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10417,11 +10265,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -10429,7 +10273,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10670,11 +10514,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -10682,7 +10522,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10923,11 +10763,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -10935,7 +10771,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11176,11 +11012,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -11188,7 +11020,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11429,11 +11261,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -11441,7 +11269,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11682,11 +11510,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -11694,7 +11518,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11935,11 +11759,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -11947,7 +11767,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12188,11 +12008,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -12200,7 +12016,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12441,11 +12257,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -12453,7 +12265,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12694,11 +12506,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -12706,7 +12514,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12947,11 +12755,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -12959,7 +12763,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13200,11 +13004,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -13212,7 +13012,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13453,11 +13253,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -13465,7 +13261,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13706,11 +13502,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -13718,7 +13510,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13955,11 +13747,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -13967,7 +13755,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14208,11 +13996,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -14220,7 +14004,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14461,11 +14245,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -14473,7 +14253,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14714,11 +14494,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -14726,7 +14502,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14967,11 +14743,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -14979,7 +14751,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15220,11 +14992,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -15232,7 +15000,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15473,11 +15241,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -15485,7 +15249,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15726,11 +15490,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -15738,7 +15498,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15979,11 +15739,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -15991,7 +15747,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16232,11 +15988,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -16244,7 +15996,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16485,11 +16237,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -16497,7 +16245,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16738,11 +16486,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -16750,7 +16494,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16991,11 +16735,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -17003,7 +16743,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17244,11 +16984,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001104256</t>
@@ -17256,7 +16992,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DELIA ZAPATA OLIVELLA (IED)</t>
+          <t>COLEGIO DELIA ZAPATA OLIVELLA</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
